--- a/product_selector_out/STM32F103 - diff.xlsx
+++ b/product_selector_out/STM32F103 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1789</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="18">
@@ -1508,22 +1508,18 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1535,67 +1531,59 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32F103RF</t>
+          <t>STM32F103RG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32F103RF</t>
+          <t>STM32F103RG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -1607,18 +1595,18 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32F103RF</t>
+          <t>STM32F103VE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -1630,88 +1618,76 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32F103RG</t>
+          <t>STM32F103VE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32F103RG</t>
+          <t>STM32F103VF</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32F103RG</t>
+          <t>STM32F103VF</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32F103RG</t>
+          <t>STM32F103VB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1734,7 +1710,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32F103RG</t>
+          <t>STM32F103VB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1757,7 +1733,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32F103VE</t>
+          <t>STM32F103VG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1780,7 +1756,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32F103VE</t>
+          <t>STM32F103VG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1803,99 +1779,87 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32F103VF</t>
+          <t>STM32F103VC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32F103VF</t>
+          <t>STM32F103VC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32F103VF</t>
+          <t>STM32F103ZE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32F103VF</t>
+          <t>STM32F103ZE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -1907,18 +1871,18 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32F103VF</t>
+          <t>STM32F103ZF</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -1930,18 +1894,18 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32F103VB</t>
+          <t>STM32F103ZF</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -1953,18 +1917,18 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32F103VB</t>
+          <t>STM32F103ZG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -1976,88 +1940,76 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32F103VG</t>
+          <t>STM32F103ZG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32F103VG</t>
+          <t>STM32F103V8</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32F103VG</t>
+          <t>STM32F103V8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32F103VG</t>
+          <t>STM32F103RD</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2080,7 +2032,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32F103VG</t>
+          <t>STM32F103RD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2103,7 +2055,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32F103VC</t>
+          <t>STM32F103ZC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2126,7 +2078,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32F103VC</t>
+          <t>STM32F103ZC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2149,7 +2101,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32F103ZE</t>
+          <t>STM32F103ZD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2172,7 +2124,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32F103ZE</t>
+          <t>STM32F103ZD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2195,99 +2147,87 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32F103ZF</t>
+          <t>STM32F103C8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32F103ZF</t>
+          <t>STM32F103C8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32F103ZF</t>
+          <t>STM32F103VD</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32F103ZF</t>
+          <t>STM32F103VD</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -2296,434 +2236,8 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>STM32F103ZF</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>STM32F103ZG</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>STM32F103ZG</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>STM32F103ZG</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>STM32F103ZG</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>STM32F103ZG</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>STM32F103V8</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>STM32F103V8</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>STM32F103RD</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>STM32F103RD</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>STM32F103ZC</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>STM32F103ZC</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>STM32F103ZD</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>STM32F103ZD</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>STM32F103C8</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>STM32F103C8</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>STM32F103VD</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>STM32F103VD</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A18:E103"/>
+  <autoFilter ref="A18:E85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F103 - diff.xlsx
+++ b/product_selector_out/STM32F103 - diff.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1856</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1795</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="18">
